--- a/ayesha_footwear_sales_2026_10.xlsx
+++ b/ayesha_footwear_sales_2026_10.xlsx
@@ -46,10 +46,10 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">BILL-1791833979061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 October 2026, 01:09</t>
+    <t xml:space="preserve">BILL-1792334672293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18 October 2026, 20:14</t>
   </si>
   <si>
     <t xml:space="preserve">Rahul Verma</t>

--- a/ayesha_footwear_sales_2026_10.xlsx
+++ b/ayesha_footwear_sales_2026_10.xlsx
@@ -46,10 +46,10 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">BILL-1792334672293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18 October 2026, 20:14</t>
+    <t xml:space="preserve">BILL-1792476909341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 October 2026, 11:45</t>
   </si>
   <si>
     <t xml:space="preserve">Rahul Verma</t>
